--- a/20251229_new_progress/Code/paper_data_newdata/main_paper_results/01_model_performance/04_graphsage_gnn/outputs/graphsage_gnn_performance.xlsx
+++ b/20251229_new_progress/Code/paper_data_newdata/main_paper_results/01_model_performance/04_graphsage_gnn/outputs/graphsage_gnn_performance.xlsx
@@ -634,43 +634,43 @@
         <v>0.0008661710550540999</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.645117335352006</v>
+        <v>0.6386071158213474</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.0126163007757757</v>
+        <v>0.0062899555118367</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.6625443441404723</v>
+        <v>0.6580855247737147</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.0096191170224093</v>
+        <v>0.0068417506669622</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.663021582733813</v>
+        <v>0.6517985611510791</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.0232613414422575</v>
+        <v>0.0046401483443445</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.6626631316820681</v>
+        <v>0.6549175423227628</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.0153057641641564</v>
+        <v>0.0052834358053952</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0.6994773254878526</v>
+        <v>0.6973820304778542</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.0142360603322619</v>
+        <v>0.0098554457084891</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>5.549774770204643</v>
+        <v>1.356465996625054</v>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
@@ -720,43 +720,43 @@
         <v>0.0008661710550540999</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.7380772142316426</v>
+        <v>0.7392884178652537</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.0118924068957792</v>
+        <v>0.0113358404525873</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.766942467087923</v>
+        <v>0.7661410018969599</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.0120014988455644</v>
+        <v>0.0167385280148406</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.7415384615384615</v>
+        <v>0.7468531468531469</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.0162478721470854</v>
+        <v>0.0160199396512182</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.7539369008475573</v>
+        <v>0.7561565937029477</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.0118680776734422</v>
+        <v>0.0099682387308379</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>0.8125779501027026</v>
+        <v>0.8187371044796787</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.0077230320193899</v>
+        <v>0.0103790403728461</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>23.4</v>
+        <v>21.4</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>6.829348431585549</v>
+        <v>6.651315659326356</v>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>3961</v>
@@ -870,19 +870,19 @@
         <v>1321</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.6525359576078729</v>
+        <v>0.6358819076457229</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.6671388101983002</v>
+        <v>0.656891495601173</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.6776978417266187</v>
+        <v>0.6446043165467625</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.6723768736616702</v>
+        <v>0.6506899055918663</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.7136989449973568</v>
+        <v>0.700804468246489</v>
       </c>
     </row>
     <row r="3">
@@ -895,7 +895,7 @@
         <v>52</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>3961</v>
@@ -907,19 +907,19 @@
         <v>1321</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.6298258894776685</v>
+        <v>0.631339894019682</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.6484149855907781</v>
+        <v>0.6494252873563219</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.6474820143884892</v>
+        <v>0.6503597122302158</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.6479481641468683</v>
+        <v>0.6498921639108555</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.6846967154710737</v>
+        <v>0.6880157216080171</v>
       </c>
     </row>
     <row r="4">
@@ -944,19 +944,19 @@
         <v>1321</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.6623769871309614</v>
+        <v>0.6464799394398183</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.6717241379310345</v>
+        <v>0.6661807580174927</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.7007194244604317</v>
+        <v>0.6575539568345323</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.6859154929577465</v>
+        <v>0.6618392469225199</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.7121681568483234</v>
+        <v>0.7133403820074931</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +969,7 @@
         <v>72</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>3961</v>
@@ -981,19 +981,19 @@
         <v>1321</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.6495079485238455</v>
+        <v>0.6457229371688115</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.6715976331360947</v>
+        <v>0.6656934306569343</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.6532374100719425</v>
+        <v>0.6561151079136691</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.662290299051787</v>
+        <v>0.6608695652173913</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.7067897120003678</v>
+        <v>0.6987542234582941</v>
       </c>
     </row>
     <row r="6">
@@ -1006,7 +1006,7 @@
         <v>82</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>3961</v>
@@ -1018,19 +1018,19 @@
         <v>1321</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.631339894019682</v>
+        <v>0.6336109008327026</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.6522366522366523</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.6359712230215827</v>
+        <v>0.6503597122302158</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.6447848285922684</v>
+        <v>0.6512968299711815</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.6800330981221413</v>
+        <v>0.6859953570689774</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1043,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>3961</v>
@@ -1055,19 +1055,19 @@
         <v>1321</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.7464042392127176</v>
+        <v>0.7433762301286904</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.7722063037249284</v>
+        <v>0.7589531680440771</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.7538461538461538</v>
+        <v>0.7706293706293706</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.7629157820240623</v>
+        <v>0.7647467036780013</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.816956311015717</v>
+        <v>0.8248794110180249</v>
       </c>
     </row>
     <row r="8">
@@ -1080,7 +1080,7 @@
         <v>52</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>3961</v>
@@ -1092,19 +1092,19 @@
         <v>1321</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7305071915215746</v>
+        <v>0.7312641937925813</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.7667161961367014</v>
+        <v>0.7654867256637168</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.7216783216783217</v>
+        <v>0.7258741258741259</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.7435158501440923</v>
+        <v>0.7451543431442929</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.8023887004085024</v>
+        <v>0.8062290844469062</v>
       </c>
     </row>
     <row r="9">
@@ -1117,7 +1117,7 @@
         <v>62</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>3961</v>
@@ -1129,19 +1129,19 @@
         <v>1321</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.7320211960635882</v>
+        <v>0.7395912187736563</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7517433751743375</v>
+        <v>0.7594405594405594</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.7538461538461538</v>
+        <v>0.7594405594405594</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.7527932960893855</v>
+        <v>0.7594405594405594</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.8132544023633133</v>
+        <v>0.8207689999769208</v>
       </c>
     </row>
     <row r="10">
@@ -1154,7 +1154,7 @@
         <v>72</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>3961</v>
@@ -1166,19 +1166,19 @@
         <v>1321</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.7570022710068131</v>
+        <v>0.7577592732778198</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7863372093023255</v>
+        <v>0.7978883861236803</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.7566433566433567</v>
+        <v>0.7398601398601399</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.7712045616535994</v>
+        <v>0.7677793904208998</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.8241339518567241</v>
+        <v>0.8337672228761337</v>
       </c>
     </row>
     <row r="11">
@@ -1191,7 +1191,7 @@
         <v>82</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>3961</v>
@@ -1206,16 +1206,16 @@
         <v>0.7244511733535201</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7577092511013216</v>
+        <v>0.7489361702127659</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.7216783216783217</v>
+        <v>0.7384615384615385</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.7392550143266475</v>
+        <v>0.7436619718309859</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.8061563848692561</v>
+        <v>0.8080408040804081</v>
       </c>
     </row>
   </sheetData>
